--- a/vse-loti/340020698/spec-340020698.xlsx
+++ b/vse-loti/340020698/spec-340020698.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -455,35 +455,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>D×s, мм</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -498,20 +503,21 @@
           <t>Соль для промышленных целей</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" s="2" t="n">
         <v>4000000</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Килограмм</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="3" t="n">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" s="3" t="n">
         <v>33200000</v>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -519,7 +525,7 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="G3" s="5" t="n">
         <v>33200000</v>
       </c>
     </row>
@@ -529,7 +535,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="G4" s="5" t="n">
         <v>33200000</v>
       </c>
     </row>
